--- a/NewShopEntry/Pampanikal/2080/10_Chaitra 2080.xlsx
+++ b/NewShopEntry/Pampanikal/2080/10_Chaitra 2080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\NewShopEntry\Pampanikal\2080\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F248A0-F33F-4EBA-BBF2-307E6EFEEED5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46196247-92F5-4BCB-9521-0E91AB9FFD15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{B3429875-737F-40AC-B95F-7B26A6BBCF55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>Pampanikal</t>
   </si>
@@ -88,13 +88,37 @@
   </si>
   <si>
     <t xml:space="preserve">  2080/12/30</t>
+  </si>
+  <si>
+    <t>Remaining of Falgun</t>
+  </si>
+  <si>
+    <t>Total Remaining Amount of theYear2080</t>
+  </si>
+  <si>
+    <t>1/25/2081Cash</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t>02/15/2081Cash</t>
+  </si>
+  <si>
+    <t>02/18/2081Cash</t>
+  </si>
+  <si>
+    <t>02/24/2081Cash</t>
+  </si>
+  <si>
+    <t>ALL PAID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +158,53 @@
     </font>
     <font>
       <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -178,43 +249,64 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -531,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9CA9EF-0BB6-4207-9984-1065795131B6}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.88671875" customWidth="1"/>
@@ -542,35 +634,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -671,7 +763,7 @@
         <v>570</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
@@ -693,7 +785,7 @@
         <v>1160</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
@@ -704,7 +796,7 @@
         <v>2195</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
@@ -715,7 +807,7 @@
         <v>680</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
@@ -730,48 +822,147 @@
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="21"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="21">
         <f>SUM(B4:B16,E4:E15)</f>
         <v>13200</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="E17" s="21"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="20">
+        <v>20025</v>
+      </c>
+      <c r="E18" s="20"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="17">
+        <f>D17+D18</f>
+        <v>33225</v>
+      </c>
+      <c r="E19" s="17"/>
+    </row>
+    <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+    </row>
+    <row r="21" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="15">
+        <v>10000</v>
+      </c>
+      <c r="E21" s="15"/>
+    </row>
+    <row r="22" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A22" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="15"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="15">
+        <f>D19-D21</f>
+        <v>23225</v>
+      </c>
+      <c r="E22" s="15"/>
+    </row>
+    <row r="23" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A23" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="15">
+        <v>7000</v>
+      </c>
+      <c r="E23" s="15"/>
+    </row>
+    <row r="24" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A24" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="15"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="15">
+        <v>9500</v>
+      </c>
+      <c r="E24" s="15"/>
+    </row>
+    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="13">
+        <f>D22-D23-D24</f>
+        <v>6725</v>
+      </c>
+      <c r="E25" s="13"/>
+    </row>
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="13">
+        <v>6725</v>
+      </c>
+      <c r="E26" s="13"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
+  <mergeCells count="21">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B17:E17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="D19:E20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
